--- a/supplementary/S6_Table.xlsx
+++ b/supplementary/S6_Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer admissibility" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reference matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Layer admissibility" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5833,7 +5833,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>reported separately</t>
+          <t>exploratory characterization; not used for validation</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Measures evolutionary constraint rather than the quantity ranked here, so it characterizes the selected positions instead of scoring them. Reported in the main text for that reason.</t>
+          <t>Estimates evolutionary constraint from observed against expected counts, which is a different quantity from the one ranked here. Ranking its sites by effect magnitude coincides with ranking them by constraint, so the reference cannot separate whether a site has a measurable effect from whether it is constrained. Examined while candidate references were being surveyed and not used to validate the integrated score; the characterization it yields is written to results/functional_benchmark/fitness_characterisation.csv.</t>
         </is>
       </c>
     </row>
